--- a/OMOP Analysis/Results/SecondaryCareAnalysis/AE/Overall/Output_Costs_OMOP.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/AE/Overall/Output_Costs_OMOP.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -363,55 +363,50 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>n_patients</t>
+          <t>mean_attendance_costs</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>mean_attendance_costs</t>
+          <t>min_attendance_costs</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>min_attendance_costs</t>
+          <t>median_attendance_costs</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>median_attendance_costs</t>
+          <t>max_attendance_costs</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>max_attendance_costs</t>
+          <t>sd_attendance_costs</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>sd_attendance_costs</t>
+          <t>q1_attendance_costs</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>q1_attendance_costs</t>
+          <t>q3_attendance_costs</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>q3_attendance_costs</t>
+          <t>se</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>ci_lower</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>ci_lower</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ci_upper</t>
         </is>
@@ -422,36 +417,33 @@
         <v>15480</v>
       </c>
       <c r="B2">
-        <v>15480</v>
+        <v>520.5</v>
       </c>
       <c r="C2">
-        <v>520.5</v>
+        <v>280.17</v>
       </c>
       <c r="D2">
         <v>280.17</v>
       </c>
       <c r="E2">
+        <v>22413.6</v>
+      </c>
+      <c r="F2">
+        <v>461.51</v>
+      </c>
+      <c r="G2">
         <v>280.17</v>
       </c>
-      <c r="F2">
-        <v>22413.6</v>
-      </c>
-      <c r="G2">
-        <v>461.51</v>
-      </c>
       <c r="H2">
-        <v>280.17</v>
+        <v>560.34</v>
       </c>
       <c r="I2">
-        <v>560.34</v>
+        <v>3.71</v>
       </c>
       <c r="J2">
-        <v>3.71</v>
+        <v>513.23</v>
       </c>
       <c r="K2">
-        <v>513.23</v>
-      </c>
-      <c r="L2">
         <v>527.78</v>
       </c>
     </row>
@@ -462,7 +454,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -473,55 +465,50 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>n_patients</t>
+          <t>mean_attendance_costs</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>mean_attendance_costs</t>
+          <t>min_attendance_costs</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>min_attendance_costs</t>
+          <t>median_attendance_costs</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>median_attendance_costs</t>
+          <t>max_attendance_costs</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>max_attendance_costs</t>
+          <t>sd_attendance_costs</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>sd_attendance_costs</t>
+          <t>q1_attendance_costs</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>q1_attendance_costs</t>
+          <t>q3_attendance_costs</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>q3_attendance_costs</t>
+          <t>se</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>ci_lower</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>ci_lower</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ci_upper</t>
         </is>
@@ -532,36 +519,33 @@
         <v>22900</v>
       </c>
       <c r="B2">
-        <v>22900</v>
+        <v>351.85</v>
       </c>
       <c r="C2">
-        <v>351.85</v>
+        <v>0</v>
       </c>
       <c r="D2">
+        <v>280.17</v>
+      </c>
+      <c r="E2">
+        <v>22413.6</v>
+      </c>
+      <c r="F2">
+        <v>450.91</v>
+      </c>
+      <c r="G2">
         <v>0</v>
       </c>
-      <c r="E2">
-        <v>280.17</v>
-      </c>
-      <c r="F2">
-        <v>22413.6</v>
-      </c>
-      <c r="G2">
-        <v>450.91</v>
-      </c>
       <c r="H2">
-        <v>0</v>
+        <v>560.34</v>
       </c>
       <c r="I2">
-        <v>560.34</v>
+        <v>2.98</v>
       </c>
       <c r="J2">
-        <v>2.98</v>
+        <v>346.01</v>
       </c>
       <c r="K2">
-        <v>346.01</v>
-      </c>
-      <c r="L2">
         <v>357.69</v>
       </c>
     </row>
